--- a/output/pdf_financials_xlsx/HFPC.U.xlsx
+++ b/output/pdf_financials_xlsx/HFPC.U.xlsx
@@ -4990,10 +4990,10 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="125">
@@ -5026,10 +5026,10 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="126">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13649,7 +13649,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -19621,7 +19625,11 @@
           <t>General and administration expenses 13, 16</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -19735,7 +19743,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -21886,7 +21894,11 @@
           <t>General and administration expenses 14</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E283" s="5" t="n">
         <v>74</v>
       </c>

--- a/output/pdf_financials_xlsx/HFPC.U.xlsx
+++ b/output/pdf_financials_xlsx/HFPC.U.xlsx
@@ -1455,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="29">
@@ -1489,13 +1489,13 @@
         <v>-42.976</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-64.94</v>
+        <v>-64.92400000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-60.808</v>
+        <v>-60.666</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>36.837</v>
+        <v>36.984</v>
       </c>
     </row>
     <row r="30">
@@ -4127,13 +4127,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="101">
@@ -12641,7 +12641,11 @@
           <t>Depreciation of property and equipment 14</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -14817,7 +14821,11 @@
           <t>Depreciation of right-of-use asset 14</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HFPC.U.xlsx
+++ b/output/pdf_financials_xlsx/HFPC.U.xlsx
@@ -4375,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.439</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="108">
@@ -12584,7 +12584,11 @@
           <t>Share-based compensation expense 9</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
